--- a/backtest_runs/20260410_193731/by_symbol/STML/STML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/STML/STML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         <v>-903.9599999999986</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>119719.72</v>
@@ -863,7 +863,7 @@
         <v>-8771.760000000004</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>110947.96</v>
@@ -909,7 +909,7 @@
         <v>-4185</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>106762.96</v>
@@ -1093,7 +1093,7 @@
         <v>-4218.480000000005</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>102544.48</v>
@@ -1415,7 +1415,7 @@
         <v>-2711.879999999996</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>103816.72</v>
